--- a/Results/Regression_OLS_Results.xlsx
+++ b/Results/Regression_OLS_Results.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,7 +514,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-12-12</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:41:19</t>
+          <t>18:15:33</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="9">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -580,7 +580,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WINSOR (percentile = 0.025)</t>
+          <t>TARGET: WINSOR (percentile = 0.025)</t>
         </is>
       </c>
     </row>
@@ -592,108 +592,132 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>92 companies winsorized</t>
+          <t>92 companies winsorised</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.05870778970935464</v>
+          <t>Feature Outlier Handling</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>none (p=0.025)</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adj. R-squared</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.04814334290474587</v>
+          <t>Feature Affected</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0 observations affected</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F-statistic</t>
+          <t>R-squared</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.557109690186803</v>
+        <v>0.05645363004324244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
+          <t>Adj. R-squared</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.914423499151075e-14</v>
+        <v>0.04639901364998478</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log-Likelihood</t>
+          <t>F-statistic</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-600.7786478991788</v>
+        <v>5.614697551375373</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AIC</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1243.557295798358</v>
+        <v>9.624586902034274e-14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BIC</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1358.998647485627</v>
+        <v>-602.9349343092015</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>No. Observations</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1803</v>
+        <v>1245.869868618403</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DF Residuals</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1782</v>
+        <v>1355.814013082469</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>No. Observations</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DF Residuals</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>DF Model</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>20</v>
+      <c r="B24" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -707,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -754,47 +778,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2657975169314506</v>
+        <v>0.264047133746281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02574001483716017</v>
+        <v>0.02574962615797231</v>
       </c>
       <c r="D2" t="n">
-        <v>10.32623790673678</v>
+        <v>10.25440649609314</v>
       </c>
       <c r="E2" t="n">
-        <v>2.559897707168867e-24</v>
+        <v>5.172299493591671e-24</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2153137258392371</v>
+        <v>0.2135445112590238</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3162813080236641</v>
+        <v>0.3145497562335382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Starting_INT</t>
+          <t>Starting_Size_ln</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01717256469674553</v>
+        <v>0.01332639001243246</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009327217695127054</v>
+        <v>0.008287108287600813</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.841124036990927</v>
+        <v>1.608086868174684</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06576951841456651</v>
+        <v>0.1079931985022029</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.03546600052307629</v>
+        <v>-0.002927077078395447</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001120871129585234</v>
+        <v>0.02957985710326037</v>
       </c>
     </row>
     <row r="4">
@@ -804,472 +828,447 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01870240926524505</v>
+        <v>0.01880817269251679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009104600127230559</v>
+        <v>0.009112794563838969</v>
       </c>
       <c r="D4" t="n">
-        <v>2.054171408287204</v>
+        <v>2.063930286231914</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0401046900767062</v>
+        <v>0.03916871872545705</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008455924098916684</v>
+        <v>0.000935290933454784</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03655922612059843</v>
+        <v>0.0366810544515788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Starting_Size_ln</t>
+          <t>Starting_ROS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01207648958831433</v>
+        <v>0.02454757864808996</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008301603880913264</v>
+        <v>0.008840253783449555</v>
       </c>
       <c r="D5" t="n">
-        <v>1.454717637886835</v>
+        <v>2.776795694943415</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1459235621985284</v>
+        <v>0.005547186106764499</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.004205413849025407</v>
+        <v>0.007209229858941679</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02835839302565406</v>
+        <v>0.04188592743723824</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Starting_Profit</t>
+          <t>Starting_INT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02452702910777609</v>
+        <v>-0.0163316148483646</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008832170377682708</v>
+        <v>0.009326864102223846</v>
       </c>
       <c r="D6" t="n">
-        <v>2.777010412950303</v>
+        <v>-1.75102957107208</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00554357121440879</v>
+        <v>0.08011276967792161</v>
       </c>
       <c r="F6" t="n">
-        <v>0.007204527661737174</v>
+        <v>-0.03462435020129037</v>
       </c>
       <c r="G6" t="n">
-        <v>0.041849530553815</v>
+        <v>0.001961120504561164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Starting_INT_Mult_Starting_Size_ln</t>
+          <t>Foreign</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01755628554131318</v>
+        <v>-0.04388374196658845</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008498625281693853</v>
+        <v>0.01719520708563279</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.065779459547375</v>
+        <v>-2.552091507130197</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03899356944580713</v>
+        <v>0.01079059531018433</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.03422460628651489</v>
+        <v>-0.07760862195934354</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0008879647961114803</v>
+        <v>-0.01015886197383336</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Foreign</t>
+          <t>Sector_chemia</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.04546829802142812</v>
+        <v>0.00362606546424601</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01719658869253416</v>
+        <v>0.05152887953614866</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.644030094245844</v>
+        <v>0.07036957715531626</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008264415617451852</v>
+        <v>0.9439073964980293</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.07919590061003626</v>
+        <v>-0.09743728723999358</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.01174069543281998</v>
+        <v>0.1046894181684856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sector_chemia</t>
+          <t>Sector_energetyka</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001496160937014918</v>
+        <v>0.3919820556740194</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05149205305832202</v>
+        <v>0.06962254771044835</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02905615232160785</v>
+        <v>5.630102151737176</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9768230599895287</v>
+        <v>2.088176288762623e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09949500266373998</v>
+        <v>0.2554316754063352</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1024873245377698</v>
+        <v>0.5285324359417036</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sector_energetyka</t>
+          <t>Sector_górnictwo i hutnictwo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3764397559646601</v>
+        <v>0.03420450528177108</v>
       </c>
       <c r="C10" t="n">
-        <v>0.06996455160993409</v>
+        <v>0.06351003746299126</v>
       </c>
       <c r="D10" t="n">
-        <v>5.38043548200501</v>
+        <v>0.5385684948100183</v>
       </c>
       <c r="E10" t="n">
-        <v>8.413739592258823e-08</v>
+        <v>0.5902518599101668</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2392185527259914</v>
+        <v>-0.09035743695644524</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5136609592033287</v>
+        <v>0.1587664475199874</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sector_górnictwo i hutnictwo</t>
+          <t>Sector_handel detaliczny</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03679302996408715</v>
+        <v>0.06492771941941279</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06346429593871819</v>
+        <v>0.04762141264416624</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5797437664732765</v>
+        <v>1.363414393112646</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5621607107183935</v>
+        <v>0.1729240707338323</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08767924708212695</v>
+        <v>-0.02847193657262631</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1612653070103012</v>
+        <v>0.1583273754114519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sector_handel detaliczny</t>
+          <t>Sector_handel hurtowy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05353699300711213</v>
+        <v>0.001171315560068666</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04789629394297435</v>
+        <v>0.03495460587369818</v>
       </c>
       <c r="D12" t="n">
-        <v>1.11776900882673</v>
+        <v>0.03350961999975031</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2638163293485951</v>
+        <v>0.9732719451820133</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0404018222113463</v>
+        <v>-0.0673849909975584</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1474758082255705</v>
+        <v>0.06972762211769573</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sector_handel hurtowy</t>
+          <t>Sector_media, telekomunkacja, IT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0003199621040368565</v>
+        <v>0.04193053279058907</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03492505335909699</v>
+        <v>0.04146012527942423</v>
       </c>
       <c r="D13" t="n">
-        <v>0.009161391988353697</v>
+        <v>1.011346022425029</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9926913944947943</v>
+        <v>0.3119880674900333</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.06817840935453938</v>
+        <v>-0.03938501883783248</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06881833356261309</v>
+        <v>0.1232460844190106</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sector_media, telekomunkacja, IT</t>
+          <t>Sector_motoryzacja</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.03969445285241681</v>
+        <v>0.05996632195335975</v>
       </c>
       <c r="C14" t="n">
-        <v>0.04143632909850013</v>
+        <v>0.03414811031527255</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9579625829802002</v>
+        <v>1.756065603622586</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3382115736433877</v>
+        <v>0.07924888215064678</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.04157445841553323</v>
+        <v>-0.007008208601969566</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1209633641203668</v>
+        <v>0.1269408525086891</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sector_motoryzacja</t>
+          <t>Sector_ochrona zdrowia i farmacja</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.06396022052108728</v>
+        <v>0.08362703686208928</v>
       </c>
       <c r="C15" t="n">
-        <v>0.03417160084048205</v>
+        <v>0.04427573439210016</v>
       </c>
       <c r="D15" t="n">
-        <v>1.871736147793099</v>
+        <v>1.888778086016577</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06140681834838416</v>
+        <v>0.05908374230012799</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.003060407440125257</v>
+        <v>-0.003210755874486326</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1309808484822998</v>
+        <v>0.1704648295986649</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sector_ochrona zdrowia i farmacja</t>
+          <t>Sector_paliwa</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08151723378224433</v>
+        <v>0.008943914252755938</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04424700975203032</v>
+        <v>0.04935151285088292</v>
       </c>
       <c r="D16" t="n">
-        <v>1.842321870767862</v>
+        <v>0.1812287756969121</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06559412561464732</v>
+        <v>0.8562086069339108</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0052642545311119</v>
+        <v>-0.08784897925927279</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1682987220956006</v>
+        <v>0.1057368077647847</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sector_paliwa</t>
+          <t>Sector_produkcja</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.003523655308130764</v>
+        <v>0.01616801909468705</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04937611935815341</v>
+        <v>0.03101957326069292</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07136355294695527</v>
+        <v>0.5212199071472939</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9431164240561174</v>
+        <v>0.6022783160855055</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0933175357475395</v>
+        <v>-0.04467052622980766</v>
       </c>
       <c r="G17" t="n">
-        <v>0.100364846363801</v>
+        <v>0.07700656441918176</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sector_produkcja</t>
+          <t>Sector_transport</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01469291755437662</v>
+        <v>0.06240305995492162</v>
       </c>
       <c r="C18" t="n">
-        <v>0.03099941500320711</v>
+        <v>0.04184913136673546</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4739740266987792</v>
+        <v>1.491143493709975</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6355764947381124</v>
+        <v>0.1361007134447526</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.04610611464911046</v>
+        <v>-0.01967544751030308</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0754919497578637</v>
+        <v>0.1444815674201463</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sector_transport</t>
+          <t>Sector_usługi</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.05819584720520814</v>
+        <v>0.06271649544607397</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0418604115326193</v>
+        <v>0.0413674221974221</v>
       </c>
       <c r="D19" t="n">
-        <v>1.390235907257138</v>
+        <v>1.516084206232756</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1646308671359422</v>
+        <v>0.1296753203881779</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.02390481529308858</v>
+        <v>-0.01841723805710427</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1402965097035049</v>
+        <v>0.1438502289492522</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sector_usługi</t>
+          <t>Sector_żywność</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06016525460657037</v>
+        <v>0.1660747828515501</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0413480180963938</v>
+        <v>0.03442882259335255</v>
       </c>
       <c r="D20" t="n">
-        <v>1.455094037791807</v>
+        <v>4.823713689343984</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1458193551736049</v>
+        <v>1.528957861646358e-06</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.02093045263606406</v>
+        <v>0.09854969260574456</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1412609618492048</v>
+        <v>0.2335998730973557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sector_żywność</t>
+          <t>HGX_Increased Export Intensity</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1623004936838109</v>
+        <v>0.052557238422296</v>
       </c>
       <c r="C21" t="n">
-        <v>0.03444580838192693</v>
+        <v>0.01654106720967363</v>
       </c>
       <c r="D21" t="n">
-        <v>4.711763239354458</v>
+        <v>3.17737892942961</v>
       </c>
       <c r="E21" t="n">
-        <v>2.646209195625155e-06</v>
+        <v>0.001511584413639874</v>
       </c>
       <c r="F21" t="n">
-        <v>0.09474206353694356</v>
+        <v>0.02011531993767136</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2298589238306783</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>HGX_Increased Export Intensity</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.05394936134801798</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0.01653966624235656</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3.261816807999344</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.001127920911429647</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.02151017820859653</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.08638854448743943</v>
+        <v>0.08499915690692064</v>
       </c>
     </row>
   </sheetData>
@@ -1283,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1305,17 +1304,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.35563218889085</v>
+        <v>10.34441052164101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Starting_INT</t>
+          <t>Starting_Size_ln</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.359763118406805</v>
+        <v>1.071445089007443</v>
       </c>
     </row>
     <row r="4">
@@ -1325,187 +1324,177 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.2956293684886</v>
+        <v>1.295588398848136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Starting_Size_ln</t>
+          <t>Starting_ROS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.077167011255711</v>
+        <v>1.219251662836079</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Starting_Profit</t>
+          <t>Starting_INT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.219253209497824</v>
+        <v>1.357172930242851</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Starting_INT_Mult_Starting_Size_ln</t>
+          <t>Foreign</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.058463664946099</v>
+        <v>1.152164275414866</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Foreign</t>
+          <t>Sector_chemia</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.154461175104393</v>
+        <v>1.246679355262265</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sector_chemia</t>
+          <t>Sector_energetyka</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.247179390802587</v>
+        <v>1.156188510156853</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sector_energetyka</t>
+          <t>Sector_górnictwo i hutnictwo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.169715046863663</v>
+        <v>1.164297393798588</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sector_górnictwo i hutnictwo</t>
+          <t>Sector_handel detaliczny</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.1647514514921</v>
+        <v>1.338391661865356</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sector_handel detaliczny</t>
+          <t>Sector_handel hurtowy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.356368311167029</v>
+        <v>1.704591477421736</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sector_handel hurtowy</t>
+          <t>Sector_media, telekomunkacja, IT</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.704828865295444</v>
+        <v>1.418125241493373</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sector_media, telekomunkacja, IT</t>
+          <t>Sector_motoryzacja</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.419093642534692</v>
+        <v>1.986988282317652</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sector_motoryzacja</t>
+          <t>Sector_ochrona zdrowia i farmacja</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.993369201539745</v>
+        <v>1.358498449951974</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sector_ochrona zdrowia i farmacja</t>
+          <t>Sector_paliwa</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.359222616858975</v>
+        <v>1.281336436128098</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sector_paliwa</t>
+          <t>Sector_produkcja</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.28496495624476</v>
+        <v>2.398904213035257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sector_produkcja</t>
+          <t>Sector_transport</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.40017775228062</v>
+        <v>1.417914744722206</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sector_transport</t>
+          <t>Sector_usługi</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.421279034536363</v>
+        <v>1.41179059561121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sector_usługi</t>
+          <t>Sector_żywność</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.413051213640456</v>
+        <v>1.775720274081746</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sector_żywność</t>
+          <t>HGX_Increased Export Intensity</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.780730159384497</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>HGX_Increased Export Intensity</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1.029344869511996</v>
+        <v>1.027636055948398</v>
       </c>
     </row>
   </sheetData>
@@ -1546,10 +1535,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9777172803878784</v>
+        <v>0.9776289463043213</v>
       </c>
       <c r="C2" t="n">
-        <v>3.86665961149717e-16</v>
+        <v>3.562091709955145e-16</v>
       </c>
     </row>
     <row r="3">
@@ -1559,10 +1548,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90.52279682741485</v>
+        <v>89.40841106981809</v>
       </c>
       <c r="C3" t="n">
-        <v>2.204065139924332e-20</v>
+        <v>3.847779870560653e-20</v>
       </c>
     </row>
   </sheetData>
@@ -1587,22 +1576,22 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Starting_Size_ln</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Starting_BS_Strength</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Starting_ROS</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Starting_INT</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Starting_BS_Strength</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Starting_Size_ln</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Starting_Profit</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1626,16 +1615,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.054</v>
+        <v>0.0527</v>
       </c>
       <c r="D2" t="n">
         <v>0.0707</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0527</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.054</v>
       </c>
       <c r="G2" t="n">
         <v>0.065</v>
@@ -1647,29 +1636,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Starting_INT</t>
+          <t>Starting_Size_ln</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.054</v>
+        <v>0.0527</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1963</v>
+        <v>-0.0488</v>
       </c>
       <c r="E3" t="n">
+        <v>-0.0403</v>
+      </c>
+      <c r="F3" t="n">
         <v>-0.0135</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.06759999999999999</v>
-      </c>
       <c r="G3" t="n">
-        <v>-0.2951</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="4">
@@ -1682,16 +1671,16 @@
         <v>0.0707</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1963</v>
+        <v>-0.0488</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0488</v>
+        <v>0.3831</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3831</v>
+        <v>0.1963</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0612</v>
@@ -1703,57 +1692,57 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Starting_Size_ln</t>
+          <t>Starting_ROS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0527</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0135</v>
+        <v>-0.0403</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0488</v>
+        <v>0.3831</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0403</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0771</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0168</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Starting_Profit</t>
+          <t>Starting_INT</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.054</v>
       </c>
       <c r="C6" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1963</v>
+      </c>
+      <c r="E6" t="n">
         <v>0.06759999999999999</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3831</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-0.0403</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0771</v>
+        <v>-0.2951</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0242</v>
+        <v>0.07439999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1766,16 +1755,16 @@
         <v>0.065</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2951</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="D7" t="n">
         <v>-0.0612</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0771</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0771</v>
+        <v>-0.2951</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -1794,16 +1783,16 @@
         <v>0.0573</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0168</v>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0168</v>
+        <v>0.0242</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0242</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0975</v>
@@ -1851,7 +1840,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Starting_Profit</t>
+          <t>Starting_ROS</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1870,22 +1859,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.2951431314772977</v>
+        <v>-0.2951431314772984</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Starting_BS_Strength</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Starting_INT</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Starting_BS_Strength</t>
-        </is>
-      </c>
       <c r="C4" t="n">
-        <v>0.1963341894807637</v>
+        <v>0.1963341894807642</v>
       </c>
     </row>
     <row r="5">
@@ -1921,7 +1910,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Starting_Profit</t>
+          <t>Starting_ROS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1945,7 +1934,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.074444887077668</v>
+        <v>0.07444488707766792</v>
       </c>
     </row>
     <row r="9">
@@ -1971,7 +1960,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Starting_Profit</t>
+          <t>Starting_ROS</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1981,16 +1970,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Starting_ROS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Starting_INT</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Starting_Profit</t>
-        </is>
-      </c>
       <c r="C11" t="n">
-        <v>0.06762916572438893</v>
+        <v>0.06762916572438898</v>
       </c>
     </row>
   </sheetData>
